--- a/data/Data_table.xlsx
+++ b/data/Data_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Никита\Downloads\timeline_coursework\timeline\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\Code\timeline\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3138FB1-814A-44AB-BCD5-799116452D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4717C3D3-C8DB-4341-B025-7C5DA4BD6C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{9693B31C-05A3-48C7-B33A-FFAC911DB34F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{9693B31C-05A3-48C7-B33A-FFAC911DB34F}"/>
   </bookViews>
   <sheets>
     <sheet name="1939" sheetId="2" r:id="rId1"/>
@@ -2041,41 +2041,41 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="321">
     <cellStyle name="20% - Accent1" xfId="12" xr:uid="{3BD75EE2-B3C8-4BBB-974D-32420E0A8553}"/>
@@ -2731,408 +2731,408 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03F7CBD-350C-412D-9640-CB598FE9C1E3}">
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="14"/>
+    <col min="1" max="1" width="16.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.53125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.86328125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:3" ht="1.8" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-    </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+    </row>
+    <row r="3" spans="1:3" ht="6.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+    </row>
+    <row r="4" spans="1:3" ht="1.8" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+    </row>
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+    </row>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A7" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>11</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>241</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A9" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>1201</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>343</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>6264</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A12" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>45</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A13" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>133</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A14" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>539</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A15" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>6</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A16" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>17530</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A17" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>10</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A18" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>1138</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A19" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>49</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>298</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A21" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>39</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A22" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>29</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A23" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>5807</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A24" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>176</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A25" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>83095</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="18">
         <v>677</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="18" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-    </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="21"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A28" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>4758</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A29" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>131</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A30" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>1648</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="18">
         <v>3619463</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="20"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A33" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>36</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A34" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>88241</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A35" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>459</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A36" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <v>198</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A37" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>28187</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="9" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A38" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>839</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A39" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>34</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A40" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <v>4895</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="9" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3155,19 +3155,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6069E6A-B078-4329-8167-CC034A2DF3C9}">
   <dimension ref="A1:B115"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="34.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.53125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="90" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="78" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3175,207 +3175,207 @@
         <v>880589</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>75</v>
+    <row r="3" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="B3" s="6">
-        <v>862238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B12" s="6">
         <v>3930</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="6">
-        <v>2982</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
-        <v>2344</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="6">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="6">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="6">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="6">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+    <row r="13" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A26" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B26" s="6">
         <v>382</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="6">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="6">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="6">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="6">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="6">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="6">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="6">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="6">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="27" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B27" s="6">
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="30.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="6">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="6">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="6">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="6">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="6">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
         <v>27</v>
       </c>
@@ -3383,39 +3383,39 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A29" s="5" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="B29" s="6">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="B30" s="6">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="B31" s="6">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A32" s="5" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A33" s="5" t="s">
         <v>32</v>
       </c>
@@ -3423,71 +3423,71 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A34" s="5" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="B34" s="6">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A35" s="5" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B35" s="6">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A36" s="5" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="B36" s="6">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A37" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="6">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="30.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>3</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A38" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="B38" s="6">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A39" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="6">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A40" s="5" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="B40" s="6">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" s="6">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
@@ -3495,593 +3495,593 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A43" s="5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B43" s="6">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A44" s="5" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B44" s="6">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A45" s="5" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="B45" s="6">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B46" s="6">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A47" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B47" s="6">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A48" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A49" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="B48" s="6">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="B49" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A50" s="5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B50" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A51" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A52" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A53" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A54" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54" s="6">
+    <row r="55" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A55" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A56" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A57" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A58" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A59" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A60" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A61" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A62" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A63" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A64" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A65" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A66" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A67" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A68" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A69" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A70" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A71" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A72" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A73" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A74" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A75" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A76" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6">
+        <v>862238</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A77" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A78" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A79" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A80" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B56" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B58" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B61" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B62" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B63" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B66" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B67" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B68" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B69" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B71" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B72" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B73" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B74" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B79" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A81" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B81" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A82" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="B82" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A83" s="5" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="B83" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A84" s="5" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="B84" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A85" s="5" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B85" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A86" s="5" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="B86" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A87" s="5" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B87" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A88" s="5" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="B88" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A89" s="5" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B89" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A90" s="5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B90" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A91" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B91" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A92" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A93" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B92" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="B93" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A94" s="5" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="B94" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A95" s="5" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="B95" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A96" s="5" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="B96" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A97" s="5" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="B97" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A98" s="5" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B98" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A99" s="5" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="B99" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A100" s="5" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="B100" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A101" s="5" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="B101" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A102" s="5" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="B102" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A103" s="5" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="B103" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A104" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A105" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A106" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A107" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A108" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="6">
         <v>68</v>
       </c>
-      <c r="B104" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B105" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B106" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B107" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B108" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A109" s="5" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="B109" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A110" s="5" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B110" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A111" s="5" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B111" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A112" s="5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B112" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A113" s="5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B113" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A114" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B114" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A115" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B115" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B115">
-    <sortCondition descending="1" ref="B2:B115"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B115">
+    <sortCondition ref="A3:A115"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4090,440 +4090,440 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45ACBD6C-B2C0-4BCA-A817-B69F11D0832F}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.53125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.46484375" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:3" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-    </row>
-    <row r="5" spans="1:3" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" spans="1:3" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+    <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A2" s="22"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+    </row>
+    <row r="3" spans="1:3" ht="4.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="22"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+    </row>
+    <row r="4" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="22"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+    </row>
+    <row r="5" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="22"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+    </row>
+    <row r="6" spans="1:3" ht="14.25" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="22"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A7" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>662</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A9" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>1086</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A10" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>328</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>7519</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A12" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>133</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+      <c r="A13" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>3590813</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A14" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A15" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>209</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A16" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>744</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A17" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-    </row>
-    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+      <c r="A18" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>3147</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A19" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>18274</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A20" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A21" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A22" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>361</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>202</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A25" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>151</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A26" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A27" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>5177</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A28" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>1993</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A29" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>63891</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="s">
+    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+      <c r="A30" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="18">
         <v>62</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+    <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+      <c r="A31" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A32" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>682</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A33" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>131</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A34" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>1040</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
+    <row r="35" spans="1:3" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A35" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="18">
         <v>3381991</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="18" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+    <row r="36" spans="1:3" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A36" s="20"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A37" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>179</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A38" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>66996</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="9" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A39" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>333</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A40" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <v>761</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
+    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+      <c r="A41" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="18">
         <v>3590751</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="18" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
+    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+      <c r="A42" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A43" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>29314</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="9" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A44" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <v>1165</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="9" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A45" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A46" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>4282</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="9" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4547,557 +4547,557 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8A9840-E8BE-44E7-AF0F-511BA24A288C}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.53125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="46.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="46.46484375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="17"/>
+      <c r="G1" s="16"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="18"/>
-      <c r="K1" s="17"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="J1" s="17"/>
+      <c r="K1" s="16"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="11" t="s">
         <v>196</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="11" t="s">
         <v>195</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="11" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="11">
         <v>84759</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="11">
         <v>131893</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="11">
         <v>15</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="11">
         <v>84297</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="11">
         <v>125177</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19" t="s">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="11">
         <v>150</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="11">
         <v>0</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="11">
         <v>1</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="11">
         <v>716</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="11">
         <v>6718</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="11">
         <v>182</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="11">
         <v>0</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="11">
         <v>11</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="11">
         <v>16</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A6" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11">
         <v>838</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="11">
         <v>12</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="11">
         <v>45</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="11">
         <v>1</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A7" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="11">
         <v>6</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="11">
         <v>0</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="11">
         <v>90</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="11">
         <v>977</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="11">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19" t="s">
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="11">
         <v>4</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="11">
         <v>0</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="11">
         <v>1</v>
       </c>
       <c r="H8" s="2"/>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="11">
         <v>762</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="11">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19" t="s">
+    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="11">
         <v>10</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="11">
         <v>0</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="11">
         <v>1</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="11">
         <v>7</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="11">
         <v>44</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="11">
         <v>1</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="11">
         <v>1</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="11">
         <v>0</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19" t="s">
+    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="11">
         <v>71</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="11">
         <v>7</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="11">
         <v>0</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="11">
         <v>0</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A12" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="11">
         <v>0</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="11">
         <v>0</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="11">
         <v>0</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="11">
         <v>15</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="11">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19" t="s">
+    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="11">
         <v>35</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="11">
         <v>0</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="11">
         <v>4</v>
       </c>
       <c r="H13" s="2"/>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="11">
         <v>2</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19" t="s">
+    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="11">
         <v>1</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="11">
         <v>0</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="11">
         <v>21</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="11">
         <v>44</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19" t="s">
+    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="11">
         <v>2</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="11">
         <v>0</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="11">
         <v>1</v>
       </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="11">
         <v>2333</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A16" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11">
         <v>534</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="11">
         <v>10</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="11">
         <v>19</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="19" t="s">
+      <c r="I16" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="11">
         <v>881</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="11">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
+    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="11">
         <v>31</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="11">
         <v>0</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="11">
         <v>4</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="11">
         <v>0</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="11">
         <v>23</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="11">
         <v>0</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="11">
         <v>0</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="19" t="s">
+      <c r="I18" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="11">
         <v>2</v>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A19" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="11">
         <v>7</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="11">
         <v>0</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="11">
         <v>13</v>
       </c>
       <c r="H19" s="2"/>
@@ -5105,22 +5105,22 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19" t="s">
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="11">
         <v>15</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="11">
         <v>0</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="11">
         <v>0</v>
       </c>
       <c r="H20" s="2"/>
@@ -5128,22 +5128,22 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19" t="s">
+    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="11">
         <v>5</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="11">
         <v>0</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="11">
         <v>1</v>
       </c>
       <c r="H21" s="2"/>
@@ -5151,15 +5151,15 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19" t="s">
+    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="11">
         <v>3</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="11">
         <v>1</v>
       </c>
       <c r="E22" s="2"/>
@@ -5170,15 +5170,15 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11">
         <v>2225</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="11">
         <v>5</v>
       </c>
       <c r="E23" s="2"/>
@@ -5189,15 +5189,15 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
+    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A24" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19">
+      <c r="B24" s="11"/>
+      <c r="C24" s="11">
         <v>3</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="11">
         <v>0</v>
       </c>
       <c r="E24" s="2"/>
@@ -5208,17 +5208,17 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
+    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A25" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="11">
         <v>28</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="11">
         <v>0</v>
       </c>
       <c r="E25" s="2"/>
@@ -5229,15 +5229,15 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19" t="s">
+    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="11">
         <v>0</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="11">
         <v>0</v>
       </c>
       <c r="E26" s="2"/>
@@ -5248,15 +5248,15 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19" t="s">
+    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="11">
         <v>1</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="11">
         <v>0</v>
       </c>
       <c r="E27" s="2"/>
@@ -5267,15 +5267,15 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19" t="s">
+    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="11">
         <v>33</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="11">
         <v>5</v>
       </c>
       <c r="E28" s="2"/>
@@ -5286,15 +5286,15 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19" t="s">
+    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="11">
         <v>5</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="11">
         <v>0</v>
       </c>
       <c r="E29" s="2"/>
@@ -5305,15 +5305,15 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19" t="s">
+    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="19">
+      <c r="C30" s="11">
         <v>5</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="11">
         <v>0</v>
       </c>
       <c r="E30" s="2"/>
@@ -5324,15 +5324,15 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19" t="s">
+    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="11">
         <v>60</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="11">
         <v>2</v>
       </c>
       <c r="E31" s="2"/>
@@ -5343,15 +5343,15 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19" t="s">
+    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="11">
         <v>20</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="11">
         <v>0</v>
       </c>
       <c r="E32" s="2"/>
@@ -5362,7 +5362,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
